--- a/Excel/Excel Workbook/COUNTIF Example.xlsx
+++ b/Excel/Excel Workbook/COUNTIF Example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801A111A-DE52-4023-AD69-189F4D04B3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA700B1F-DD16-47A9-9F34-BB1103339C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
